--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/94.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/94.xlsx
@@ -426,13 +426,13 @@
         <v>-11.41407359460117</v>
       </c>
       <c r="E2">
-        <v>-12.1712858220254</v>
+        <v>-11.96502288792403</v>
       </c>
       <c r="F2">
-        <v>-4.204919824070426</v>
+        <v>-3.88716223019355</v>
       </c>
       <c r="G2">
-        <v>-9.345283874202801</v>
+        <v>-9.914648048774355</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.75709858050051</v>
       </c>
       <c r="E3">
-        <v>-13.87476188949076</v>
+        <v>-12.29696003268627</v>
       </c>
       <c r="F3">
-        <v>-4.028227400318486</v>
+        <v>-4.187268971451575</v>
       </c>
       <c r="G3">
-        <v>-9.100147908656387</v>
+        <v>-9.983136614890798</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.997511595110733</v>
       </c>
       <c r="E4">
-        <v>-11.89103667958671</v>
+        <v>-13.44937515510623</v>
       </c>
       <c r="F4">
-        <v>-3.766463301033843</v>
+        <v>-3.991718763774904</v>
       </c>
       <c r="G4">
-        <v>-8.781296025587022</v>
+        <v>-9.384553565389636</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.213428464504011</v>
       </c>
       <c r="E5">
-        <v>-12.72912136418626</v>
+        <v>-14.06115840812048</v>
       </c>
       <c r="F5">
-        <v>-3.299149771153335</v>
+        <v>-3.742401713084726</v>
       </c>
       <c r="G5">
-        <v>-8.2826451037343</v>
+        <v>-8.526400571790836</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.402167282162464</v>
       </c>
       <c r="E6">
-        <v>-14.00555327578029</v>
+        <v>-14.75699466719109</v>
       </c>
       <c r="F6">
-        <v>-3.934706377277228</v>
+        <v>-4.195395255673038</v>
       </c>
       <c r="G6">
-        <v>-7.960625028583851</v>
+        <v>-8.986318110834086</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.5780190320212</v>
       </c>
       <c r="E7">
-        <v>-14.47488885040926</v>
+        <v>-15.44944362770396</v>
       </c>
       <c r="F7">
-        <v>-3.577865580968868</v>
+        <v>-4.0590343840286</v>
       </c>
       <c r="G7">
-        <v>-7.15240499335388</v>
+        <v>-8.875153302170899</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.75573055367657</v>
       </c>
       <c r="E8">
-        <v>-15.53629975917108</v>
+        <v>-16.27666903163312</v>
       </c>
       <c r="F8">
-        <v>-3.388396418396148</v>
+        <v>-3.924988799274987</v>
       </c>
       <c r="G8">
-        <v>-6.993111473640768</v>
+        <v>-8.37385063334122</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.94938678181752</v>
       </c>
       <c r="E9">
-        <v>-16.59648345147682</v>
+        <v>-16.79148407072112</v>
       </c>
       <c r="F9">
-        <v>-3.858481665606423</v>
+        <v>-3.915080696770102</v>
       </c>
       <c r="G9">
-        <v>-7.006740989625948</v>
+        <v>-7.414335356421017</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.161147386892143</v>
       </c>
       <c r="E10">
-        <v>-17.06583714000182</v>
+        <v>-17.62904345233578</v>
       </c>
       <c r="F10">
-        <v>-3.794608740278762</v>
+        <v>-4.302498190650597</v>
       </c>
       <c r="G10">
-        <v>-6.257892278097266</v>
+        <v>-7.090845399051132</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.414439073469079</v>
       </c>
       <c r="E11">
-        <v>-17.19888823482118</v>
+        <v>-18.61929392054108</v>
       </c>
       <c r="F11">
-        <v>-3.606142730630832</v>
+        <v>-4.200090442112105</v>
       </c>
       <c r="G11">
-        <v>-5.794707230606756</v>
+        <v>-6.530277343977421</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.720252294854888</v>
       </c>
       <c r="E12">
-        <v>-18.49981919079671</v>
+        <v>-18.92877436269928</v>
       </c>
       <c r="F12">
-        <v>-3.704725078503195</v>
+        <v>-3.980193688099754</v>
       </c>
       <c r="G12">
-        <v>-5.980577809909136</v>
+        <v>-6.328092396257512</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.085415114768607</v>
       </c>
       <c r="E13">
-        <v>-18.58939240666843</v>
+        <v>-18.75813240514224</v>
       </c>
       <c r="F13">
-        <v>-3.332089800925658</v>
+        <v>-3.802184988544766</v>
       </c>
       <c r="G13">
-        <v>-5.693791870933152</v>
+        <v>-6.139285363061798</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.52972675864321</v>
       </c>
       <c r="E14">
-        <v>-20.3565207047856</v>
+        <v>-20.13167291335675</v>
       </c>
       <c r="F14">
-        <v>-3.628571606429031</v>
+        <v>-3.696972387980395</v>
       </c>
       <c r="G14">
-        <v>-5.198868623357649</v>
+        <v>-5.639479060815869</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.057929033181734</v>
       </c>
       <c r="E15">
-        <v>-21.23489069415739</v>
+        <v>-21.93646000132171</v>
       </c>
       <c r="F15">
-        <v>-3.17112227558106</v>
+        <v>-3.740788053384072</v>
       </c>
       <c r="G15">
-        <v>-4.33999062028575</v>
+        <v>-4.732207503050904</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.666890467555382</v>
       </c>
       <c r="E16">
-        <v>-21.54557571040163</v>
+        <v>-22.37309546514129</v>
       </c>
       <c r="F16">
-        <v>-3.063388953009971</v>
+        <v>-3.297472327162666</v>
       </c>
       <c r="G16">
-        <v>-4.2319311033384</v>
+        <v>-4.980839404686788</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.360357717866233</v>
       </c>
       <c r="E17">
-        <v>-22.36180597944016</v>
+        <v>-22.76552396569798</v>
       </c>
       <c r="F17">
-        <v>-3.093439637281328</v>
+        <v>-3.196665812813786</v>
       </c>
       <c r="G17">
-        <v>-3.506805761144135</v>
+        <v>-4.619691991807694</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.127468039331027</v>
       </c>
       <c r="E18">
-        <v>-23.5197503686235</v>
+        <v>-23.98730172449344</v>
       </c>
       <c r="F18">
-        <v>-2.286598189810971</v>
+        <v>-2.742828163842021</v>
       </c>
       <c r="G18">
-        <v>-3.027044812138493</v>
+        <v>-4.498171796697666</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.9520744674610448</v>
       </c>
       <c r="E19">
-        <v>-23.29777815818952</v>
+        <v>-24.96872619685778</v>
       </c>
       <c r="F19">
-        <v>-2.390965855624486</v>
+        <v>-2.59084593971559</v>
       </c>
       <c r="G19">
-        <v>-3.286740556966622</v>
+        <v>-4.064258592865392</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.8240468991548942</v>
       </c>
       <c r="E20">
-        <v>-24.71584715132146</v>
+        <v>-25.01518834017648</v>
       </c>
       <c r="F20">
-        <v>-1.64503260654717</v>
+        <v>-2.189106801808094</v>
       </c>
       <c r="G20">
-        <v>-3.872693875235465</v>
+        <v>-4.627974976746951</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.7276119132514218</v>
       </c>
       <c r="E21">
-        <v>-25.46681758143545</v>
+        <v>-26.25515697906075</v>
       </c>
       <c r="F21">
-        <v>-1.95345864163151</v>
+        <v>-1.85636569834938</v>
       </c>
       <c r="G21">
-        <v>-3.847480760408375</v>
+        <v>-4.012216816988049</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.6498220853852771</v>
       </c>
       <c r="E22">
-        <v>-25.28526200151993</v>
+        <v>-26.66624732100306</v>
       </c>
       <c r="F22">
-        <v>-1.766569015151108</v>
+        <v>-1.852883241788011</v>
       </c>
       <c r="G22">
-        <v>-2.701429484532397</v>
+        <v>-4.410256949356781</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.5865649101519792</v>
       </c>
       <c r="E23">
-        <v>-27.10455379173146</v>
+        <v>-27.15023250904683</v>
       </c>
       <c r="F23">
-        <v>-0.5924394016882834</v>
+        <v>-1.589280166869153</v>
       </c>
       <c r="G23">
-        <v>-3.793902891400811</v>
+        <v>-4.314628530909394</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.5349922848977532</v>
       </c>
       <c r="E24">
-        <v>-27.30027443834297</v>
+        <v>-27.70802729494163</v>
       </c>
       <c r="F24">
-        <v>-1.271007328467735</v>
+        <v>-1.407427842565174</v>
       </c>
       <c r="G24">
-        <v>-3.091123731596627</v>
+        <v>-3.752448240158057</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.4955120390398343</v>
       </c>
       <c r="E25">
-        <v>-26.62076332807001</v>
+        <v>-27.62674571497795</v>
       </c>
       <c r="F25">
-        <v>-0.714398277667649</v>
+        <v>-1.370360886392105</v>
       </c>
       <c r="G25">
-        <v>-3.427888976578988</v>
+        <v>-3.84627903237762</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.4728201714727295</v>
       </c>
       <c r="E26">
-        <v>-26.96903015010391</v>
+        <v>-27.90408304862971</v>
       </c>
       <c r="F26">
-        <v>-1.031481580478647</v>
+        <v>-1.18494409715388</v>
       </c>
       <c r="G26">
-        <v>-3.337643505178455</v>
+        <v>-4.392489251447513</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.4706609590151604</v>
       </c>
       <c r="E27">
-        <v>-27.01323258489278</v>
+        <v>-28.23761421624264</v>
       </c>
       <c r="F27">
-        <v>-0.8749209697169428</v>
+        <v>-1.219644407657152</v>
       </c>
       <c r="G27">
-        <v>-2.387020353576734</v>
+        <v>-4.54040111559661</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.4913971698813651</v>
       </c>
       <c r="E28">
-        <v>-27.60464676182052</v>
+        <v>-27.25740337491236</v>
       </c>
       <c r="F28">
-        <v>-0.8858902108648138</v>
+        <v>-0.6766595155309091</v>
       </c>
       <c r="G28">
-        <v>-4.122924770366817</v>
+        <v>-4.44982790018769</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.5359127695280037</v>
       </c>
       <c r="E29">
-        <v>-26.64668884176393</v>
+        <v>-27.92360982855078</v>
       </c>
       <c r="F29">
-        <v>-0.7373548235014317</v>
+        <v>-1.003496016142468</v>
       </c>
       <c r="G29">
-        <v>-3.237228037881282</v>
+        <v>-4.4816687271844</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.6026551212663614</v>
       </c>
       <c r="E30">
-        <v>-26.01132582459174</v>
+        <v>-27.484488232501</v>
       </c>
       <c r="F30">
-        <v>-1.036566927964433</v>
+        <v>-1.147806729751573</v>
       </c>
       <c r="G30">
-        <v>-3.060378695173415</v>
+        <v>-4.043802731978236</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.6875352181067753</v>
       </c>
       <c r="E31">
-        <v>-26.5543396713255</v>
+        <v>-27.33564634881689</v>
       </c>
       <c r="F31">
-        <v>-1.235837333647076</v>
+        <v>-1.135333173400218</v>
       </c>
       <c r="G31">
-        <v>-3.039379904817818</v>
+        <v>-4.352898437343368</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.7850779107828896</v>
       </c>
       <c r="E32">
-        <v>-25.99048578720845</v>
+        <v>-27.15579800360226</v>
       </c>
       <c r="F32">
-        <v>-1.070468692291405</v>
+        <v>-1.027922085748817</v>
       </c>
       <c r="G32">
-        <v>-3.1184092479313</v>
+        <v>-4.350034815451899</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.8888020906374703</v>
       </c>
       <c r="E33">
-        <v>-26.75906292426427</v>
+        <v>-27.05560551618255</v>
       </c>
       <c r="F33">
-        <v>-0.9160345006526879</v>
+        <v>-0.8685193464281082</v>
       </c>
       <c r="G33">
-        <v>-3.800557087934746</v>
+        <v>-4.519157344871107</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.9905684054916987</v>
       </c>
       <c r="E34">
-        <v>-24.80686495040162</v>
+        <v>-26.2560173891222</v>
       </c>
       <c r="F34">
-        <v>-1.07933802207318</v>
+        <v>-1.523637020401708</v>
       </c>
       <c r="G34">
-        <v>-4.142546373778077</v>
+        <v>-4.45677342472908</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.082086506901718</v>
       </c>
       <c r="E35">
-        <v>-23.78732884078872</v>
+        <v>-25.97403836961259</v>
       </c>
       <c r="F35">
-        <v>-1.164201777387781</v>
+        <v>-1.310406967247088</v>
       </c>
       <c r="G35">
-        <v>-3.10673626435983</v>
+        <v>-4.981852431621805</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.155830561480806</v>
       </c>
       <c r="E36">
-        <v>-23.62311278784857</v>
+        <v>-25.79331602891448</v>
       </c>
       <c r="F36">
-        <v>-1.103306004505781</v>
+        <v>-1.259840107510595</v>
       </c>
       <c r="G36">
-        <v>-4.12840703377985</v>
+        <v>-5.020244828240733</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.204971294430011</v>
       </c>
       <c r="E37">
-        <v>-25.72918830849186</v>
+        <v>-25.44496769434844</v>
       </c>
       <c r="F37">
-        <v>-1.486604855659557</v>
+        <v>-1.391639159867816</v>
       </c>
       <c r="G37">
-        <v>-3.554815292554645</v>
+        <v>-4.728512934229077</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.225408722185817</v>
       </c>
       <c r="E38">
-        <v>-23.74051800497143</v>
+        <v>-24.1507569938003</v>
       </c>
       <c r="F38">
-        <v>-1.245580591038804</v>
+        <v>-1.586988902633009</v>
       </c>
       <c r="G38">
-        <v>-3.473730100661276</v>
+        <v>-4.522179872948461</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.215392111418636</v>
       </c>
       <c r="E39">
-        <v>-22.72997997321178</v>
+        <v>-23.65060968202315</v>
       </c>
       <c r="F39">
-        <v>-1.1293507040172</v>
+        <v>-1.589731627103678</v>
       </c>
       <c r="G39">
-        <v>-3.597508087829087</v>
+        <v>-4.958715028847839</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.175631698456808</v>
       </c>
       <c r="E40">
-        <v>-22.23045759084768</v>
+        <v>-23.88011727320589</v>
       </c>
       <c r="F40">
-        <v>-1.575986526789026</v>
+        <v>-1.623205125483403</v>
       </c>
       <c r="G40">
-        <v>-2.438999229088831</v>
+        <v>-4.550319510032266</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.10982583523155</v>
       </c>
       <c r="E41">
-        <v>-22.32647029675831</v>
+        <v>-23.18973329684051</v>
       </c>
       <c r="F41">
-        <v>-1.077183438458498</v>
+        <v>-1.549015712521277</v>
       </c>
       <c r="G41">
-        <v>-4.002960531660247</v>
+        <v>-4.656938939670034</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.024486640055031</v>
       </c>
       <c r="E42">
-        <v>-21.16104486851431</v>
+        <v>-21.45114344191968</v>
       </c>
       <c r="F42">
-        <v>-1.65883900604963</v>
+        <v>-2.045342810684837</v>
       </c>
       <c r="G42">
-        <v>-3.678699217179712</v>
+        <v>-4.625584762867597</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.9276705399444232</v>
       </c>
       <c r="E43">
-        <v>-20.05033246323098</v>
+        <v>-21.28181927029888</v>
       </c>
       <c r="F43">
-        <v>-1.273355750054671</v>
+        <v>-1.964407173594311</v>
       </c>
       <c r="G43">
-        <v>-3.743092638464077</v>
+        <v>-4.60840303151878</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.8285804710518524</v>
       </c>
       <c r="E44">
-        <v>-19.76592165317924</v>
+        <v>-20.53530938708243</v>
       </c>
       <c r="F44">
-        <v>-1.56041156288159</v>
+        <v>-1.678251796134236</v>
       </c>
       <c r="G44">
-        <v>-5.356943862312309</v>
+        <v>-4.535163832553483</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.7376431760916086</v>
       </c>
       <c r="E45">
-        <v>-19.72830814807153</v>
+        <v>-19.82456992005258</v>
       </c>
       <c r="F45">
-        <v>-1.510712003815828</v>
+        <v>-1.78263685766321</v>
       </c>
       <c r="G45">
-        <v>-4.512049603598292</v>
+        <v>-4.694834754458071</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.6644226517867113</v>
       </c>
       <c r="E46">
-        <v>-19.70854135902805</v>
+        <v>-18.81895433953926</v>
       </c>
       <c r="F46">
-        <v>-1.638429689979455</v>
+        <v>-1.934707717101741</v>
       </c>
       <c r="G46">
-        <v>-5.31696571438007</v>
+        <v>-4.212524685387192</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.6183592056669864</v>
       </c>
       <c r="E47">
-        <v>-18.37283172267362</v>
+        <v>-18.87073291134296</v>
       </c>
       <c r="F47">
-        <v>-1.069082005259119</v>
+        <v>-2.045483633143313</v>
       </c>
       <c r="G47">
-        <v>-4.418745188119472</v>
+        <v>-4.919567827845957</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.6073968866396138</v>
       </c>
       <c r="E48">
-        <v>-16.50400748376619</v>
+        <v>-17.92961638612089</v>
       </c>
       <c r="F48">
-        <v>-1.607843880365889</v>
+        <v>-1.898260379745965</v>
       </c>
       <c r="G48">
-        <v>-4.023187964905194</v>
+        <v>-4.121620415424344</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.6358172233830507</v>
       </c>
       <c r="E49">
-        <v>-16.38537505018725</v>
+        <v>-17.55747997759257</v>
       </c>
       <c r="F49">
-        <v>-1.617853043693916</v>
+        <v>-1.755448182768525</v>
       </c>
       <c r="G49">
-        <v>-4.631997289577165</v>
+        <v>-4.738368428299488</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.7051504341700605</v>
       </c>
       <c r="E50">
-        <v>-16.67423282171452</v>
+        <v>-17.321578181111</v>
       </c>
       <c r="F50">
-        <v>-1.832530254701227</v>
+        <v>-2.037269541977153</v>
       </c>
       <c r="G50">
-        <v>-3.838505871451412</v>
+        <v>-4.736706534438773</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.8147730182869931</v>
       </c>
       <c r="E51">
-        <v>-16.03094950350292</v>
+        <v>-16.07636556932585</v>
       </c>
       <c r="F51">
-        <v>-1.728335717674897</v>
+        <v>-2.090014179615606</v>
       </c>
       <c r="G51">
-        <v>-3.981276458378021</v>
+        <v>-5.385583391772544</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.960608300562749</v>
       </c>
       <c r="E52">
-        <v>-16.03727125321763</v>
+        <v>-16.05075704881247</v>
       </c>
       <c r="F52">
-        <v>-1.536705344548273</v>
+        <v>-2.102825709867303</v>
       </c>
       <c r="G52">
-        <v>-5.574413598787033</v>
+        <v>-5.546416315161417</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.138372552623154</v>
       </c>
       <c r="E53">
-        <v>-14.80616483796637</v>
+        <v>-15.83529678400152</v>
       </c>
       <c r="F53">
-        <v>-1.478476086335885</v>
+        <v>-2.089273619157503</v>
       </c>
       <c r="G53">
-        <v>-4.467195022086706</v>
+        <v>-5.812729840522548</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.34412940342811</v>
       </c>
       <c r="E54">
-        <v>-13.61580563183614</v>
+        <v>-15.48167730569056</v>
       </c>
       <c r="F54">
-        <v>-2.118608593992842</v>
+        <v>-2.356374889618384</v>
       </c>
       <c r="G54">
-        <v>-4.444732970602751</v>
+        <v>-5.392482568676385</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.570777819379477</v>
       </c>
       <c r="E55">
-        <v>-12.11040048899227</v>
+        <v>-14.52890901684676</v>
       </c>
       <c r="F55">
-        <v>-1.086828948496696</v>
+        <v>-2.11040858507253</v>
       </c>
       <c r="G55">
-        <v>-5.370556825569792</v>
+        <v>-5.735743104006796</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.81256414731207</v>
       </c>
       <c r="E56">
-        <v>-13.13451035735291</v>
+        <v>-14.22066937656666</v>
       </c>
       <c r="F56">
-        <v>-1.396679775513851</v>
+        <v>-2.157755580714341</v>
       </c>
       <c r="G56">
-        <v>-5.616364831860678</v>
+        <v>-5.949279912380867</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.065746374615093</v>
       </c>
       <c r="E57">
-        <v>-11.91792675824426</v>
+        <v>-13.24506399330217</v>
       </c>
       <c r="F57">
-        <v>-2.320306116165688</v>
+        <v>-2.222203393019545</v>
       </c>
       <c r="G57">
-        <v>-4.903796388896869</v>
+        <v>-6.030090328994477</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.323888961177324</v>
       </c>
       <c r="E58">
-        <v>-12.09110013277158</v>
+        <v>-11.91357036624888</v>
       </c>
       <c r="F58">
-        <v>-1.435671029163623</v>
+        <v>-2.19652069006315</v>
       </c>
       <c r="G58">
-        <v>-6.786685717085053</v>
+        <v>-5.963084887279628</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.582642656521065</v>
       </c>
       <c r="E59">
-        <v>-11.21987154690989</v>
+        <v>-13.71887822872472</v>
       </c>
       <c r="F59">
-        <v>-2.240270914442005</v>
+        <v>-2.272262463538123</v>
       </c>
       <c r="G59">
-        <v>-5.427551177573885</v>
+        <v>-6.409458984521719</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.839679199609308</v>
       </c>
       <c r="E60">
-        <v>-10.73219112407585</v>
+        <v>-12.19953444288525</v>
       </c>
       <c r="F60">
-        <v>-1.284807101030972</v>
+        <v>-2.530973200576047</v>
       </c>
       <c r="G60">
-        <v>-5.754596660852946</v>
+        <v>-6.720233136475263</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.089023745422338</v>
       </c>
       <c r="E61">
-        <v>-12.41872164180451</v>
+        <v>-11.66291932992432</v>
       </c>
       <c r="F61">
-        <v>-1.550666648755056</v>
+        <v>-2.273292952587205</v>
       </c>
       <c r="G61">
-        <v>-5.630772326047586</v>
+        <v>-6.751153631812056</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.326938289203742</v>
       </c>
       <c r="E62">
-        <v>-8.935582460168744</v>
+        <v>-12.28393614144021</v>
       </c>
       <c r="F62">
-        <v>-1.770531096438698</v>
+        <v>-2.167406889324358</v>
       </c>
       <c r="G62">
-        <v>-6.57634027461084</v>
+        <v>-6.424634525273738</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.551015669944415</v>
       </c>
       <c r="E63">
-        <v>-11.60447031590732</v>
+        <v>-11.29796055269815</v>
       </c>
       <c r="F63">
-        <v>-2.359150748785166</v>
+        <v>-2.052334231564465</v>
       </c>
       <c r="G63">
-        <v>-7.362906031468438</v>
+        <v>-6.877507223409419</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.755903148458807</v>
       </c>
       <c r="E64">
-        <v>-10.16762626953959</v>
+        <v>-11.1899473906672</v>
       </c>
       <c r="F64">
-        <v>-1.967772830351886</v>
+        <v>-2.0060069561955</v>
       </c>
       <c r="G64">
-        <v>-6.454008995843691</v>
+        <v>-7.464321283518472</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.939794479072323</v>
       </c>
       <c r="E65">
-        <v>-9.370628429611628</v>
+        <v>-10.80275380606337</v>
       </c>
       <c r="F65">
-        <v>-1.82114185964754</v>
+        <v>-2.315809737903292</v>
       </c>
       <c r="G65">
-        <v>-7.641359327322077</v>
+        <v>-7.754010570932397</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.101390053950166</v>
       </c>
       <c r="E66">
-        <v>-9.675797764514526</v>
+        <v>-10.76125487025708</v>
       </c>
       <c r="F66">
-        <v>-1.802167275919014</v>
+        <v>-2.474447065743814</v>
       </c>
       <c r="G66">
-        <v>-7.407158093691876</v>
+        <v>-7.333693777629909</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.237228935577097</v>
       </c>
       <c r="E67">
-        <v>-9.116571980833305</v>
+        <v>-10.75862382685862</v>
       </c>
       <c r="F67">
-        <v>-2.107128250157444</v>
+        <v>-2.355170443414714</v>
       </c>
       <c r="G67">
-        <v>-6.811743236271797</v>
+        <v>-7.498330517843405</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.347022786944142</v>
       </c>
       <c r="E68">
-        <v>-9.695994758588734</v>
+        <v>-10.86304138052749</v>
       </c>
       <c r="F68">
-        <v>-2.112622811140213</v>
+        <v>-2.127258406412875</v>
       </c>
       <c r="G68">
-        <v>-7.128334016737839</v>
+        <v>-6.958095833471897</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.430265858482458</v>
       </c>
       <c r="E69">
-        <v>-8.786899073074903</v>
+        <v>-10.1867047305339</v>
       </c>
       <c r="F69">
-        <v>-2.248068336804557</v>
+        <v>-2.173140020119134</v>
       </c>
       <c r="G69">
-        <v>-7.952699582562836</v>
+        <v>-7.271624359314114</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.484840097921879</v>
       </c>
       <c r="E70">
-        <v>-10.37517981873314</v>
+        <v>-9.539771462272123</v>
       </c>
       <c r="F70">
-        <v>-2.096932704163788</v>
+        <v>-2.470677165693674</v>
       </c>
       <c r="G70">
-        <v>-7.131399581907204</v>
+        <v>-6.781842388961099</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.511340492545735</v>
       </c>
       <c r="E71">
-        <v>-10.54685879683793</v>
+        <v>-10.24373180371249</v>
       </c>
       <c r="F71">
-        <v>-1.963695605995307</v>
+        <v>-2.403305216456587</v>
       </c>
       <c r="G71">
-        <v>-7.13014488514782</v>
+        <v>-7.291007603446547</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.508930411284122</v>
       </c>
       <c r="E72">
-        <v>-10.40092419346675</v>
+        <v>-9.996083145655026</v>
       </c>
       <c r="F72">
-        <v>-2.566156449275151</v>
+        <v>-2.380983200053349</v>
       </c>
       <c r="G72">
-        <v>-6.613024429731504</v>
+        <v>-8.020350580657842</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.476759835881926</v>
       </c>
       <c r="E73">
-        <v>-9.35826116709668</v>
+        <v>-11.06494339415947</v>
       </c>
       <c r="F73">
-        <v>-2.55836813895403</v>
+        <v>-2.79037562439531</v>
       </c>
       <c r="G73">
-        <v>-6.532118007297256</v>
+        <v>-7.484078619296842</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.417633667955776</v>
       </c>
       <c r="E74">
-        <v>-9.090927232527868</v>
+        <v>-10.09038408839075</v>
       </c>
       <c r="F74">
-        <v>-2.369265114773347</v>
+        <v>-2.668546802098184</v>
       </c>
       <c r="G74">
-        <v>-6.470184321348571</v>
+        <v>-7.286247038961075</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.333240249724331</v>
       </c>
       <c r="E75">
-        <v>-10.64922495178132</v>
+        <v>-10.85783816389267</v>
       </c>
       <c r="F75">
-        <v>-2.490111493330753</v>
+        <v>-2.475059229254483</v>
       </c>
       <c r="G75">
-        <v>-5.99950419875715</v>
+        <v>-7.413607036402377</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.226888405226953</v>
       </c>
       <c r="E76">
-        <v>-9.33726716159712</v>
+        <v>-11.63216193446423</v>
       </c>
       <c r="F76">
-        <v>-2.096168121051003</v>
+        <v>-2.121164935797881</v>
       </c>
       <c r="G76">
-        <v>-5.797484778314204</v>
+        <v>-7.024147838071436</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.103736573011443</v>
       </c>
       <c r="E77">
-        <v>-10.70890571072841</v>
+        <v>-11.98984345396007</v>
       </c>
       <c r="F77">
-        <v>-2.068949624929817</v>
+        <v>-2.47606735238369</v>
       </c>
       <c r="G77">
-        <v>-6.41726856144886</v>
+        <v>-6.877325143404758</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.965457093019667</v>
       </c>
       <c r="E78">
-        <v>-11.85095062767081</v>
+        <v>-12.49827334469725</v>
       </c>
       <c r="F78">
-        <v>-2.989550767826631</v>
+        <v>-2.555971672057731</v>
       </c>
       <c r="G78">
-        <v>-6.056760083858845</v>
+        <v>-6.550504777222367</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.815134979446873</v>
       </c>
       <c r="E79">
-        <v>-11.66094038678297</v>
+        <v>-12.84602844916828</v>
       </c>
       <c r="F79">
-        <v>-2.243967089793297</v>
+        <v>-2.686503322288668</v>
       </c>
       <c r="G79">
-        <v>-5.253860095310483</v>
+        <v>-6.893331631087134</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.657037185959597</v>
       </c>
       <c r="E80">
-        <v>-12.73932854459955</v>
+        <v>-13.19431338509821</v>
       </c>
       <c r="F80">
-        <v>-2.894983516755637</v>
+        <v>-2.41900029363743</v>
       </c>
       <c r="G80">
-        <v>-5.330694546731428</v>
+        <v>-6.211634025277029</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.49199750999686</v>
       </c>
       <c r="E81">
-        <v>-12.84593787968813</v>
+        <v>-13.58828609529152</v>
       </c>
       <c r="F81">
-        <v>-2.932029763743636</v>
+        <v>-2.828536853907477</v>
       </c>
       <c r="G81">
-        <v>-4.964154255168861</v>
+        <v>-6.074372186127768</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.323522364500589</v>
       </c>
       <c r="E82">
-        <v>-13.82827257532801</v>
+        <v>-14.10868927130498</v>
       </c>
       <c r="F82">
-        <v>-2.641990999899237</v>
+        <v>-2.616575859613945</v>
       </c>
       <c r="G82">
-        <v>-4.817765241967829</v>
+        <v>-6.3494023778938</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.155570103987048</v>
       </c>
       <c r="E83">
-        <v>-15.07726646290957</v>
+        <v>-15.24328937697878</v>
       </c>
       <c r="F83">
-        <v>-2.545855649334743</v>
+        <v>-2.868855980503938</v>
       </c>
       <c r="G83">
-        <v>-4.368848645751577</v>
+        <v>-5.930754099543106</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.989399784921674</v>
       </c>
       <c r="E84">
-        <v>-14.90522520688416</v>
+        <v>-15.95004378688188</v>
       </c>
       <c r="F84">
-        <v>-2.620651427235719</v>
+        <v>-2.811069898852047</v>
       </c>
       <c r="G84">
-        <v>-3.753848600921168</v>
+        <v>-5.255853043725124</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.82928373250897</v>
       </c>
       <c r="E85">
-        <v>-16.73366904306519</v>
+        <v>-17.2904086945162</v>
       </c>
       <c r="F85">
-        <v>-2.795986156814471</v>
+        <v>-2.84670874962269</v>
       </c>
       <c r="G85">
-        <v>-4.945939633611791</v>
+        <v>-4.933346318380403</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.680327337052757</v>
       </c>
       <c r="E86">
-        <v>-17.7765947209277</v>
+        <v>-17.87485807842014</v>
       </c>
       <c r="F86">
-        <v>-2.466119488243471</v>
+        <v>-2.856008002086517</v>
       </c>
       <c r="G86">
-        <v>-5.451867134559832</v>
+        <v>-4.957033271713889</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.544979710316998</v>
       </c>
       <c r="E87">
-        <v>-19.5779220547508</v>
+        <v>-19.53097536471329</v>
       </c>
       <c r="F87">
-        <v>-2.605086403737116</v>
+        <v>-3.003367107737924</v>
       </c>
       <c r="G87">
-        <v>-3.760751088370549</v>
+        <v>-5.228762849577268</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.428156316921281</v>
       </c>
       <c r="E88">
-        <v>-20.14999964766579</v>
+        <v>-20.38817473809922</v>
       </c>
       <c r="F88">
-        <v>-2.566384250310921</v>
+        <v>-2.565937760280812</v>
       </c>
       <c r="G88">
-        <v>-4.698956383654464</v>
+        <v>-4.999616818985534</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.33722506025659</v>
       </c>
       <c r="E89">
-        <v>-21.79838682882784</v>
+        <v>-22.60773381737472</v>
       </c>
       <c r="F89">
-        <v>-3.088322811834236</v>
+        <v>-3.138078699883388</v>
       </c>
       <c r="G89">
-        <v>-3.337206513167272</v>
+        <v>-4.503859313934134</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.277546862973417</v>
       </c>
       <c r="E90">
-        <v>-22.58759569346261</v>
+        <v>-22.79748593524412</v>
       </c>
       <c r="F90">
-        <v>-2.35235233751039</v>
+        <v>-3.074765750920019</v>
       </c>
       <c r="G90">
-        <v>-4.55702336474929</v>
+        <v>-5.280745035634904</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.255233088942593</v>
       </c>
       <c r="E91">
-        <v>-25.01471285040568</v>
+        <v>-25.31216113712549</v>
       </c>
       <c r="F91">
-        <v>-3.527694680850913</v>
+        <v>-2.89885779109853</v>
       </c>
       <c r="G91">
-        <v>-3.878318492106687</v>
+        <v>-4.705809212920755</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.278312813413101</v>
       </c>
       <c r="E92">
-        <v>-26.18933108088525</v>
+        <v>-26.8066073728708</v>
       </c>
       <c r="F92">
-        <v>-2.343883109184168</v>
+        <v>-2.891075279349229</v>
       </c>
       <c r="G92">
-        <v>-4.459544351345451</v>
+        <v>-5.628342385621761</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.349835728313352</v>
       </c>
       <c r="E93">
-        <v>-27.87931682428176</v>
+        <v>-27.94678655852204</v>
       </c>
       <c r="F93">
-        <v>-2.569480687662585</v>
+        <v>-3.003044872818235</v>
       </c>
       <c r="G93">
-        <v>-4.603185611748888</v>
+        <v>-5.118395882389045</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.469863575902552</v>
       </c>
       <c r="E94">
-        <v>-30.5227931481263</v>
+        <v>-30.6013168874193</v>
       </c>
       <c r="F94">
-        <v>-3.010989744578485</v>
+        <v>-2.997176718136803</v>
       </c>
       <c r="G94">
-        <v>-4.745241120839014</v>
+        <v>-5.500512290713883</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.638907436457036</v>
       </c>
       <c r="E95">
-        <v>-30.52158178132924</v>
+        <v>-31.51815852772325</v>
       </c>
       <c r="F95">
-        <v>-2.853122798422567</v>
+        <v>-3.049781361684183</v>
       </c>
       <c r="G95">
-        <v>-4.012528008268741</v>
+        <v>-5.877788681460306</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.852790039803416</v>
       </c>
       <c r="E96">
-        <v>-33.75430767152586</v>
+        <v>-34.64435885960043</v>
       </c>
       <c r="F96">
-        <v>-3.318131810188486</v>
+        <v>-3.147492267048801</v>
       </c>
       <c r="G96">
-        <v>-4.811647353811256</v>
+        <v>-5.479089750529258</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.097782729959324</v>
       </c>
       <c r="E97">
-        <v>-35.7399823894902</v>
+        <v>-37.08050352947779</v>
       </c>
       <c r="F97">
-        <v>-3.284869545496475</v>
+        <v>-3.300401434298965</v>
       </c>
       <c r="G97">
-        <v>-5.417245449310133</v>
+        <v>-6.063305032389985</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.369426453411279</v>
       </c>
       <c r="E98">
-        <v>-38.1316959366413</v>
+        <v>-38.55498372332327</v>
       </c>
       <c r="F98">
-        <v>-3.299178764012433</v>
+        <v>-3.049522082687107</v>
       </c>
       <c r="G98">
-        <v>-5.183534176419744</v>
+        <v>-6.042723370772335</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.64455853448889</v>
       </c>
       <c r="E99">
-        <v>-41.20441499048789</v>
+        <v>-40.86892299362963</v>
       </c>
       <c r="F99">
-        <v>-3.659569114641789</v>
+        <v>-3.360799358371883</v>
       </c>
       <c r="G99">
-        <v>-4.885830058255244</v>
+        <v>-5.811210300120023</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.922020052521742</v>
       </c>
       <c r="E100">
-        <v>-43.51204156802756</v>
+        <v>-43.76140651773394</v>
       </c>
       <c r="F100">
-        <v>-3.450269664813452</v>
+        <v>-3.587991544100689</v>
       </c>
       <c r="G100">
-        <v>-4.892977526074531</v>
+        <v>-6.676620009540904</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.170690562131</v>
       </c>
       <c r="E101">
-        <v>-44.90788481072985</v>
+        <v>-45.65166628835667</v>
       </c>
       <c r="F101">
-        <v>-4.079162055181823</v>
+        <v>-3.797799611514345</v>
       </c>
       <c r="G101">
-        <v>-5.77351973915542</v>
+        <v>-6.322106929922509</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.415793480921001</v>
       </c>
       <c r="E102">
-        <v>-47.36548086198155</v>
+        <v>-47.3805674731381</v>
       </c>
       <c r="F102">
-        <v>-4.093078627548854</v>
+        <v>-3.597515284130675</v>
       </c>
       <c r="G102">
-        <v>-6.234764806959918</v>
+        <v>-6.784689458124872</v>
       </c>
     </row>
   </sheetData>
